--- a/InputData/elec/BDTPTUMCF/Boolean Does This Plant Type Use Maximum Capacity Factor.xlsx
+++ b/InputData/elec/BDTPTUMCF/Boolean Does This Plant Type Use Maximum Capacity Factor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\elec\BDTPTUMCF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\BDTPTUMCF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51ED9A98-533A-401F-8B39-EF71FBE64D8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97DCE9AD-342C-4F1D-9344-9510E0382F11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2370" yWindow="1695" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="12" r:id="rId1"/>
@@ -885,7 +885,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="3"/>
     </row>

--- a/InputData/elec/BDTPTUMCF/Boolean Does This Plant Type Use Maximum Capacity Factor.xlsx
+++ b/InputData/elec/BDTPTUMCF/Boolean Does This Plant Type Use Maximum Capacity Factor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27528"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\BDTPTUMCF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\elec\BDTPTUMCF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97DCE9AD-342C-4F1D-9344-9510E0382F11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51ED9A98-533A-401F-8B39-EF71FBE64D8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2370" yWindow="1695" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="12" r:id="rId1"/>
@@ -33,7 +33,7 @@
     <definedName name="Submittal">[3]Lists!$A$2:$A$3</definedName>
     <definedName name="Zone">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -46,6 +46,7 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -55,45 +56,72 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
+    <t>BDTPTUMCF Boolean Does This Plant Type Use Maximum Capacity Factor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source: </t>
+  </si>
+  <si>
+    <t>None needed</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>This file selects whether a plant type will use the maximum capacity factors set in the elec/MCF</t>
+  </si>
+  <si>
+    <t>file or hourly capacity factors set in the elec/SYSHECF file for the maximum</t>
+  </si>
+  <si>
+    <t>amount it can dispatch in any given hour. Generally, variable sources</t>
+  </si>
+  <si>
+    <t>of electricity like wind and solar should not use maximum capacity factors.</t>
+  </si>
+  <si>
+    <t>Unit: dimensionless (peak time capacity factors)</t>
+  </si>
+  <si>
+    <t>hard coal</t>
+  </si>
+  <si>
+    <t>natural gas steam turbine</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle</t>
+  </si>
+  <si>
+    <t>nuclear</t>
+  </si>
+  <si>
+    <t>hydro</t>
+  </si>
+  <si>
+    <t>onshore wind</t>
+  </si>
+  <si>
+    <t>solar pv</t>
+  </si>
+  <si>
+    <t>solar thermal</t>
+  </si>
+  <si>
+    <t>biomass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">geothermal </t>
+  </si>
+  <si>
+    <t>petroleum</t>
+  </si>
+  <si>
     <t>natural gas nonpeaker</t>
   </si>
   <si>
-    <t>nuclear</t>
-  </si>
-  <si>
-    <t>hydro</t>
-  </si>
-  <si>
-    <t>solar pv</t>
-  </si>
-  <si>
-    <t>solar thermal</t>
-  </si>
-  <si>
-    <t>biomass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">geothermal </t>
-  </si>
-  <si>
-    <t>petroleum</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source: </t>
-  </si>
-  <si>
     <t>lignite</t>
   </si>
   <si>
-    <t>hard coal</t>
-  </si>
-  <si>
-    <t>onshore wind</t>
-  </si>
-  <si>
     <t>offshore wind</t>
   </si>
   <si>
@@ -104,33 +132,6 @@
   </si>
   <si>
     <t>municipal solid waste</t>
-  </si>
-  <si>
-    <t>Unit: dimensionless (peak time capacity factors)</t>
-  </si>
-  <si>
-    <t>natural gas steam turbine</t>
-  </si>
-  <si>
-    <t>natural gas combined cycle</t>
-  </si>
-  <si>
-    <t>None needed</t>
-  </si>
-  <si>
-    <t>This file selects whether a plant type will use the maximum capacity factors set in the elec/MCF</t>
-  </si>
-  <si>
-    <t>file or hourly capacity factors set in the elec/SYSHECF file for the maximum</t>
-  </si>
-  <si>
-    <t>amount it can dispatch in any given hour. Generally, variable sources</t>
-  </si>
-  <si>
-    <t>of electricity like wind and solar should not use maximum capacity factors.</t>
-  </si>
-  <si>
-    <t>BDTPTUMCF Boolean Does This Plant Type Use Maximum Capacity Factor</t>
   </si>
   <si>
     <t>hard coal w CCS</t>
@@ -161,7 +162,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -396,63 +397,7 @@
       <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1" refreshError="1"/>
       <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3">
-        <row r="11">
-          <cell r="B11" t="str">
-            <v>CAISO System</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="B12" t="str">
-            <v>Big Creek-Ventura</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="B13" t="str">
-            <v>Bay Area</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="B14" t="str">
-            <v>Fresno</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="B15" t="str">
-            <v>Humboldt</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="B16" t="str">
-            <v>Kern</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="B17" t="str">
-            <v>LA Basin</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="B18" t="str">
-            <v>NCNB</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="B19" t="str">
-            <v>San Diego-IV</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="B20" t="str">
-            <v>Sierra</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="B21" t="str">
-            <v>Stockton</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="3"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -472,18 +417,7 @@
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2">
-        <row r="2">
-          <cell r="A2" t="str">
-            <v>Monthly</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>Annual</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="2"/>
       <sheetData sheetId="3" refreshError="1"/>
       <sheetData sheetId="4" refreshError="1"/>
       <sheetData sheetId="5" refreshError="1"/>
@@ -756,7 +690,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.28515625" customWidth="1"/>
     <col min="2" max="2" width="50.7109375" bestFit="1" customWidth="1"/>
@@ -764,54 +698,54 @@
     <col min="8" max="8" width="53.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E3" s="1"/>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="H4" s="2"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H6" s="2"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H7" s="4"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="H8" s="2"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -831,173 +765,173 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:C25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.5703125" customWidth="1"/>
     <col min="2" max="3" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="30">
       <c r="A1" s="6" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="7"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="8">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="8">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="8">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="8">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
       <c r="B4" s="8">
         <v>1</v>
       </c>
       <c r="C4" s="3"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B5" s="8">
         <v>0</v>
       </c>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B6" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" s="3"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B7" s="8">
         <v>0</v>
       </c>
       <c r="C7" s="3"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B8" s="8">
         <v>0</v>
       </c>
       <c r="C8" s="3"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B9" s="8">
         <v>0</v>
       </c>
       <c r="C9" s="3"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B10" s="8">
         <v>0</v>
       </c>
       <c r="C10" s="3"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B11" s="8">
         <v>0</v>
       </c>
       <c r="C11" s="3"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B12" s="8">
         <v>1</v>
       </c>
       <c r="C12" s="3"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="B13" s="8">
         <v>1</v>
       </c>
       <c r="C13" s="3"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B14" s="8">
         <v>1</v>
       </c>
       <c r="C14" s="3"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B15" s="8">
         <v>0</v>
       </c>
       <c r="C15" s="3"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B16" s="8">
         <v>1</v>
       </c>
       <c r="C16" s="3"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B17" s="8">
         <v>1</v>
       </c>
       <c r="C17" s="3"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B18" s="8">
         <v>0</v>
       </c>
       <c r="C18" s="3"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -1006,7 +940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -1015,7 +949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -1024,7 +958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -1033,7 +967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -1042,7 +976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24" s="10" t="s">
         <v>31</v>
       </c>
@@ -1050,7 +984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25" s="10" t="s">
         <v>32</v>
       </c>
@@ -1061,4 +995,165 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="77cd1fc208aa16a525090c2a27f33c66">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d77402130d0e9b5bbfbb66ed18db98d9" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62971E22-AC44-449E-8C2D-7F48B03A6F62}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D392E03F-1236-4ADA-A75E-4EBA94E36477}"/>
 </file>